--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487525_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487525_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6407</v>
+        <v>8.3781</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3634</v>
+        <v>5.9939</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2772</v>
+        <v>2.3842</v>
       </c>
       <c r="G2" t="n">
         <v>5.7556</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7233000000000001</v>
+        <v>0.0141</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6599</v>
+        <v>-0.0294</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0634</v>
+        <v>0.0435</v>
       </c>
       <c r="V2" t="n">
         <v>1.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4138</v>
+        <v>5.2314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1491</v>
+        <v>0.7796</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2647</v>
+        <v>4.4518</v>
       </c>
       <c r="G3" t="n">
         <v>1.8664</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4146</v>
+        <v>0.403</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6005</v>
+        <v>0.03</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1859</v>
+        <v>0.373</v>
       </c>
       <c r="V3" t="n">
         <v>2.7662</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1115</v>
+        <v>4.5752</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1219</v>
+        <v>1.7199</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9896</v>
+        <v>2.8553</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5163</v>
+        <v>5.3009</v>
       </c>
       <c r="H4" t="n">
-        <v>3.652</v>
+        <v>1.6632</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8643</v>
+        <v>3.6377</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5967</v>
+        <v>3.3084</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5321</v>
+        <v>2.0007</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0645</v>
+        <v>1.3077</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9196</v>
+        <v>1.9925</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8801</v>
+        <v>-0.3375</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7998</v>
+        <v>2.33</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.7419</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2784</v>
+        <v>1.1579</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1461</v>
+        <v>0.3699</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1323</v>
+        <v>0.788</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9412</v>
+        <v>-1.492</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.875</v>
+        <v>3.2475</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0464</v>
+        <v>0.9103</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8286</v>
+        <v>2.3371</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3009</v>
+        <v>5.5163</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6632</v>
+        <v>3.652</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6377</v>
+        <v>1.8643</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3084</v>
+        <v>4.5967</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0007</v>
+        <v>4.5321</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3077</v>
+        <v>0.0645</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9925</v>
+        <v>0.9196</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3375</v>
+        <v>-0.8801</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>1.7998</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-4.8962</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4577</v>
+        <v>1.4143</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3035</v>
+        <v>0.9345</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7612</v>
+        <v>0.4798</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.492</v>
+        <v>-0.9412</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.492</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5539</v>
+        <v>3.1772</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5004</v>
+        <v>2.1504</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0535</v>
+        <v>1.0268</v>
       </c>
       <c r="G6" t="n">
         <v>1.5955</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7832</v>
+        <v>0.4065</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8651</v>
+        <v>0.5152</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0819</v>
+        <v>-0.1087</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0517</v>
+        <v>0.3394</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4258</v>
+        <v>-0.5472</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4775</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7403</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1644</v>
+        <v>0.0892</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.7631</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2607</v>
+        <v>-0.6166</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3675</v>
+        <v>0.0204</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1068</v>
+        <v>-0.637</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.001</v>
+        <v>-0.0573</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2031</v>
+        <v>0.0687</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1261</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9792</v>
+        <v>0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2794</v>
+        <v>0.0341</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.22</v>
+        <v>0.0694</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4993</v>
+        <v>-0.0353</v>
       </c>
       <c r="V7" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0745</v>
+        <v>0.2961</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8542</v>
+        <v>0.0859</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.2102</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.7403</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0892</v>
+        <v>0.1644</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7631</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6166</v>
+        <v>0.2607</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0204</v>
+        <v>0.3675</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.637</v>
+        <v>-0.1068</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0573</v>
+        <v>-1.001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0687</v>
+        <v>-0.2031</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1261</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9792</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3798</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2376</v>
+        <v>0.2917</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1422</v>
+        <v>0.232</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.778</v>
+        <v>-1.7513</v>
       </c>
       <c r="E9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7988</v>
+        <v>-0.7721</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6802</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9798</v>
+        <v>-2.0494</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5051</v>
+        <v>-0.5481</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4746</v>
+        <v>-1.5014</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4932</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>0.101</v>
+        <v>0.0313</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4799</v>
+        <v>0.437</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3789</v>
+        <v>-0.4057</v>
       </c>
       <c r="V10" t="n">
         <v>0.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2506</v>
+        <v>-2.4285</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7592</v>
+        <v>-0.9639</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4914</v>
+        <v>-1.4647</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7517</v>
@@ -1312,13 +1312,13 @@
         <v>0.5875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5219</v>
+        <v>0.3439</v>
       </c>
       <c r="T11" t="n">
-        <v>0.504</v>
+        <v>0.2994</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3822</v>
+        <v>-6.24</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3481</v>
+        <v>-6.698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9659</v>
+        <v>0.458</v>
       </c>
       <c r="G12" t="n">
         <v>0.8038999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1433</v>
+        <v>1.2855</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7463</v>
+        <v>0.3964</v>
       </c>
       <c r="U12" t="n">
-        <v>1.397</v>
+        <v>0.8891</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0415</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.1815</v>
+        <v>12.7757</v>
       </c>
       <c r="E13" t="n">
-        <v>1.309600000000001</v>
+        <v>1.903599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.8719</v>
+        <v>10.8718</v>
       </c>
       <c r="G13" t="n">
         <v>13.4993</v>
@@ -1468,13 +1468,13 @@
         <v>13.7092</v>
       </c>
       <c r="S13" t="n">
-        <v>4.928599999999999</v>
+        <v>5.522399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7199</v>
+        <v>3.3141</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2085</v>
+        <v>2.2084</v>
       </c>
       <c r="V13" t="n">
         <v>0.6083999999999996</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>M. DOMINGUEZ ITURZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9676</v>
+        <v>1.6883</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5987</v>
+        <v>1.0468</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3689</v>
+        <v>0.6415</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3011</v>
+        <v>-3.8596</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1639</v>
+        <v>-0.3631</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1372</v>
+        <v>-3.4965</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4772</v>
+        <v>-0.5117</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7045</v>
+        <v>0.9951</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7727000000000001</v>
+        <v>-1.5069</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1761</v>
+        <v>-3.3478</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5406</v>
+        <v>-1.3582</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6355</v>
+        <v>-1.9896</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5875</v>
+        <v>1.9585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3294</v>
+        <v>3.917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8624</v>
+        <v>-0.6687</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0385</v>
+        <v>-0.7411</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1761</v>
+        <v>0.0723</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6083</v>
+        <v>4.2581</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.2581</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DOMINGUEZ ITURZA</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4216</v>
+        <v>1.5162</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4328</v>
+        <v>-0.3233</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0112</v>
+        <v>1.8395</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.8596</v>
+        <v>-0.5532</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3631</v>
+        <v>3.3018</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.4965</v>
+        <v>-3.855</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5117</v>
+        <v>0.0896</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9951</v>
+        <v>3.2987</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5069</v>
+        <v>-3.2091</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.3478</v>
+        <v>-0.6428</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3582</v>
+        <v>0.0031</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9896</v>
+        <v>-0.6459</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9585</v>
+        <v>2.9377</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.917</v>
+        <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9354</v>
+        <v>-0.2601</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3551</v>
+        <v>-0.08</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5804</v>
+        <v>-0.1801</v>
       </c>
       <c r="V15" t="n">
-        <v>4.2581</v>
+        <v>-0.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2581</v>
+        <v>-0.3329</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2046</v>
+        <v>0.3826</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9402</v>
+        <v>-0.7355</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1448</v>
+        <v>1.1181</v>
       </c>
       <c r="G16" t="n">
         <v>0.3589</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2374</v>
+        <v>0.4154</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0418</v>
+        <v>0.1629</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2792</v>
+        <v>0.2525</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>M. JUAN SEVILLANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.043</v>
+        <v>0.1118</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0397</v>
+        <v>0.5784</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0826</v>
+        <v>-0.4666</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5532</v>
+        <v>-0.8411</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3018</v>
+        <v>0.7047</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.855</v>
+        <v>-1.5458</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0896</v>
+        <v>1.1434</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2987</v>
+        <v>1.2453</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.2091</v>
+        <v>-0.102</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6428</v>
+        <v>-1.9844</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0031</v>
+        <v>-0.5406</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6459</v>
+        <v>-1.4438</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9377</v>
+        <v>2.1543</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9377</v>
+        <v>3.1336</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7333</v>
+        <v>-0.8685</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7963</v>
+        <v>-0.4693</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.3992</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6083</v>
+        <v>-0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0.8837</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4625</v>
+        <v>0.0823</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2376</v>
+        <v>-1.3457</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2249</v>
+        <v>1.428</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.676</v>
+        <v>1.3011</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2719</v>
+        <v>1.1639</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4042</v>
+        <v>0.1372</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.4772</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.7045</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.676</v>
+        <v>-1.1761</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2719</v>
+        <v>-0.5406</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4042</v>
+        <v>-0.6355</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3917</v>
+        <v>3.3294</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1782</v>
+        <v>-0.0229</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2376</v>
+        <v>0.0941</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0594</v>
+        <v>-0.117</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. JUAN SEVILLANO</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7234</v>
+        <v>-0.4625</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4761</v>
+        <v>-0.2376</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1995</v>
+        <v>-0.2249</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8411</v>
+        <v>-0.676</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7047</v>
+        <v>-0.2719</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5458</v>
+        <v>-0.4042</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1434</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2453</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.102</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9844</v>
+        <v>-0.676</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5406</v>
+        <v>-0.2719</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4438</v>
+        <v>-0.4042</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1543</v>
+        <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1336</v>
+        <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7038</v>
+        <v>-0.1782</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5717</v>
+        <v>-0.2376</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1321</v>
+        <v>0.0594</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9521</v>
+        <v>-3.0534</v>
       </c>
       <c r="E20" t="n">
         <v>-3.2031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.251</v>
+        <v>0.1497</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4576</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7186</v>
+        <v>0.6172</v>
       </c>
       <c r="T20" t="n">
         <v>0.2423</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4763</v>
+        <v>0.3749</v>
       </c>
       <c r="V20" t="n">
         <v>0.3329</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5074</v>
+        <v>-3.9469</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2186</v>
+        <v>-3.0139</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2888</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3291</v>
@@ -2092,13 +2092,13 @@
         <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5285</v>
+        <v>0.0321</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5717</v>
+        <v>-0.367</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0432</v>
+        <v>0.3991</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1729</v>
+        <v>-5.771</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7404</v>
+        <v>-3.6381</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4325</v>
+        <v>-2.1329</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4429</v>
@@ -2170,13 +2170,13 @@
         <v>2.3502</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6678</v>
+        <v>-1.2658</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9151</v>
+        <v>-0.8128</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7526</v>
+        <v>-0.453</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4332</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.1815</v>
+        <v>-9.4526</v>
       </c>
       <c r="E23" t="n">
         <v>-10.872</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3096</v>
+        <v>1.4194</v>
       </c>
       <c r="G23" t="n">
         <v>-13.4995</v>
@@ -2236,7 +2236,7 @@
         <v>-3.38</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.531600000000001</v>
+        <v>-8.531599999999999</v>
       </c>
       <c r="P23" t="n">
         <v>6.8547</v>
@@ -2248,16 +2248,16 @@
         <v>20.564</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.928599999999999</v>
+        <v>-2.1995</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2085</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.7201</v>
+        <v>0.008900000000000019</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6082999999999996</v>
+        <v>-0.6082999999999998</v>
       </c>
       <c r="W23" t="n">
         <v>6.633799999999999</v>
